--- a/test_data/toydata_metadata_template_PEGSt000000.xlsx
+++ b/test_data/toydata_metadata_template_PEGSt000000.xlsx
@@ -1,31 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueji/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueji/Documents/GitHub/PEGASUS_metadata_template/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{185E9F44-A9D5-3545-B521-E4E4C38E1223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47737BF8-FEB3-2540-8EBC-F1CF40EDBB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30080" yWindow="7600" windowWidth="20320" windowHeight="17380" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset_description" sheetId="1" r:id="rId1"/>
-    <sheet name="Genomic_identifier" sheetId="2" r:id="rId2"/>
+    <sheet name="DatasetDescription" sheetId="1" r:id="rId1"/>
+    <sheet name="genomicidentifier" sheetId="2" r:id="rId2"/>
     <sheet name="Evidence" sheetId="3" r:id="rId3"/>
     <sheet name="Integration" sheetId="4" r:id="rId4"/>
-    <sheet name="source" sheetId="5" r:id="rId5"/>
-    <sheet name="method" sheetId="6" r:id="rId6"/>
+    <sheet name="Source" sheetId="5" r:id="rId5"/>
+    <sheet name="Method" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="220">
   <si>
     <t>Identifier of the origin of the PEG list (e.g., publication, DOI, preprint, URL).</t>
   </si>
@@ -78,9 +91,6 @@
     <t>gwas_sample_ancestry</t>
   </si>
   <si>
-    <t>gws_sample_ancestry_label</t>
-  </si>
-  <si>
     <t>PMID:36357675</t>
   </si>
   <si>
@@ -211,18 +221,6 @@
   </si>
   <si>
     <t>column_description</t>
-  </si>
-  <si>
-    <t>stream_name</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>category_abbreviation</t>
-  </si>
-  <si>
-    <t>class</t>
   </si>
   <si>
     <t>source_tag</t>
@@ -688,6 +686,21 @@
 • Weak — variant-centric evidence does not support the gene.
 • Medium — variant-centric evidence supports the gene, but gene-centric evidence is lacking.
 • Strong — both variant-centric and gene-centric evidence show consistent positive support for the gene.</t>
+  </si>
+  <si>
+    <t>gwas_sample_ancestry_label</t>
+  </si>
+  <si>
+    <t>evidence_stream_tag</t>
+  </si>
+  <si>
+    <t>evidence_category</t>
+  </si>
+  <si>
+    <t>variant_or_gene_centric</t>
+  </si>
+  <si>
+    <t>evidence_category_abbreviation</t>
   </si>
 </sst>
 </file>
@@ -705,6 +718,7 @@
       <sz val="10"/>
       <color rgb="FF999999"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -716,23 +730,27 @@
       <sz val="10"/>
       <color rgb="FFCCCCCC"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCCCCCC"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -743,6 +761,7 @@
       <sz val="11"/>
       <color rgb="FFCCCCCC"/>
       <name val="Courier New"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -754,24 +773,28 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF999999"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FFCCCCCC"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1222,51 +1245,51 @@
         <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="7">
         <v>6136</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="F4" s="8">
         <v>6136</v>
@@ -1275,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
@@ -1313,114 +1336,114 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="29">
+      <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="71">
       <c r="A3" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>49</v>
       </c>
       <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>48</v>
       </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1438,256 +1461,245 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="93" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="B2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="C2" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="I2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="G3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" s="8" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>162</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" t="s">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>161</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" t="s">
         <v>72</v>
       </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" t="s">
-        <v>77</v>
-      </c>
       <c r="I6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" t="s">
         <v>173</v>
       </c>
-      <c r="B7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G7" t="s">
-        <v>178</v>
-      </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1713,132 +1725,132 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>61</v>
-      </c>
       <c r="D2" s="17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="s">
         <v>88</v>
       </c>
-      <c r="D4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" t="s">
-        <v>93</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
@@ -1871,386 +1883,386 @@
   <sheetData>
     <row r="1" spans="1:18" ht="70">
       <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B2" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="J2" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="K2" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="L2" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="M2" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="N2" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="O2" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="P2" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="Q2" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="R2" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="72" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="P4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Q4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="R4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" t="s">
         <v>130</v>
       </c>
-      <c r="C5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O5" t="s">
         <v>134</v>
       </c>
-      <c r="I5" t="s">
+      <c r="P5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q5" t="s">
         <v>135</v>
       </c>
-      <c r="J5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L5" t="s">
-        <v>136</v>
-      </c>
-      <c r="M5" t="s">
-        <v>137</v>
-      </c>
-      <c r="N5" t="s">
-        <v>138</v>
-      </c>
-      <c r="O5" t="s">
-        <v>139</v>
-      </c>
-      <c r="P5" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>140</v>
-      </c>
       <c r="R5" s="28" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" t="s">
         <v>130</v>
       </c>
-      <c r="C6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="F6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" t="s">
         <v>134</v>
       </c>
-      <c r="I6" t="s">
+      <c r="P6" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q6" t="s">
         <v>135</v>
       </c>
-      <c r="J6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K6" t="s">
-        <v>92</v>
-      </c>
-      <c r="L6" t="s">
-        <v>136</v>
-      </c>
-      <c r="M6" t="s">
-        <v>137</v>
-      </c>
-      <c r="N6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O6" t="s">
-        <v>139</v>
-      </c>
-      <c r="P6" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>140</v>
-      </c>
       <c r="R6" s="28" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D7">
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I7" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="N7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="O7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Q7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2277,138 +2289,138 @@
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14">
       <c r="A2" s="15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>149</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="14" thickTop="1">
       <c r="A4" s="25" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13">
       <c r="A5" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
